--- a/data/gravel/Rodeo Labs TrailDonkey 4.2 2025.xlsx
+++ b/data/gravel/Rodeo Labs TrailDonkey 4.2 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10824"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6531400-B287-9443-B03E-FA7A504DA739}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E77AE10-EE8E-5A48-8402-28C744EB2A8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="29460" yWindow="-19840" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="104">
   <si>
     <t>brand</t>
   </si>
@@ -326,12 +326,6 @@
     <t>Standover height at center of top tube, 700 x 40mm</t>
   </si>
   <si>
-    <t>rider_min_spec</t>
-  </si>
-  <si>
-    <t>rider_max_spec</t>
-  </si>
-  <si>
     <t>TrailDonkey 4.2</t>
   </si>
   <si>
@@ -344,10 +338,13 @@
     <t>usd</t>
   </si>
   <si>
-    <t>a8:g33</t>
-  </si>
-  <si>
     <t>Rodeo Labs</t>
+  </si>
+  <si>
+    <t>https://www.rodeo-labs.com/wp-content/uploads/2024/11/IMG_4120.jpg</t>
+  </si>
+  <si>
+    <t>a8:g31</t>
   </si>
 </sst>
 </file>
@@ -702,7 +699,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G73"/>
+  <dimension ref="A1:G71"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -713,7 +710,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
@@ -721,7 +718,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
@@ -748,6 +745,11 @@
         <v>93</v>
       </c>
     </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>102</v>
+      </c>
+    </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>5</v>
@@ -1166,6 +1168,18 @@
       <c r="C28">
         <v>38</v>
       </c>
+      <c r="D28">
+        <v>38</v>
+      </c>
+      <c r="E28">
+        <v>38</v>
+      </c>
+      <c r="F28">
+        <v>38</v>
+      </c>
+      <c r="G28">
+        <v>38</v>
+      </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
@@ -1177,24 +1191,33 @@
       <c r="C29">
         <v>55</v>
       </c>
+      <c r="D29">
+        <v>55</v>
+      </c>
+      <c r="E29">
+        <v>55</v>
+      </c>
+      <c r="F29">
+        <v>55</v>
+      </c>
+      <c r="G29">
+        <v>55</v>
+      </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>46</v>
       </c>
-      <c r="B30" t="s">
-        <v>46</v>
-      </c>
       <c r="C30">
-        <f>C32</f>
+        <f>C32*2.54</f>
         <v>162.56</v>
       </c>
       <c r="D30">
-        <f>AVERAGE(D32,C33)</f>
+        <f t="shared" ref="D30:G31" si="0">D32*2.54</f>
         <v>167.64000000000001</v>
       </c>
       <c r="E30">
-        <f t="shared" ref="E30:G30" si="0">AVERAGE(E32,D33)</f>
+        <f t="shared" si="0"/>
         <v>175.26</v>
       </c>
       <c r="F30">
@@ -1203,304 +1226,267 @@
       </c>
       <c r="G30">
         <f t="shared" si="0"/>
-        <v>186.69</v>
+        <v>185.42000000000002</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>47</v>
       </c>
-      <c r="B31" t="s">
-        <v>47</v>
-      </c>
       <c r="C31">
-        <f>D30</f>
+        <f>C33*2.54</f>
         <v>167.64000000000001</v>
       </c>
       <c r="D31">
-        <f t="shared" ref="D31:F31" si="1">E30</f>
+        <f t="shared" si="0"/>
         <v>175.26</v>
       </c>
       <c r="E31">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>182.88</v>
       </c>
       <c r="F31">
-        <f t="shared" si="1"/>
-        <v>186.69</v>
+        <f t="shared" si="0"/>
+        <v>187.96</v>
       </c>
       <c r="G31">
-        <f t="shared" ref="G31" si="2">G33</f>
+        <f t="shared" si="0"/>
         <v>193.04</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A32" s="1" t="s">
-        <v>97</v>
-      </c>
       <c r="C32">
-        <f>C34*2.54</f>
-        <v>162.56</v>
+        <v>64</v>
       </c>
       <c r="D32">
-        <f t="shared" ref="D32:G33" si="3">D34*2.54</f>
-        <v>167.64000000000001</v>
+        <v>66</v>
       </c>
       <c r="E32">
-        <f t="shared" si="3"/>
-        <v>175.26</v>
+        <v>69</v>
       </c>
       <c r="F32">
-        <f t="shared" si="3"/>
-        <v>182.88</v>
+        <v>72</v>
       </c>
       <c r="G32">
-        <f t="shared" si="3"/>
-        <v>185.42000000000002</v>
+        <v>73</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A33" s="1" t="s">
-        <v>98</v>
+      <c r="A33" t="s">
+        <v>48</v>
+      </c>
+      <c r="B33" t="s">
+        <v>49</v>
       </c>
       <c r="C33">
-        <f>C35*2.54</f>
-        <v>167.64000000000001</v>
+        <v>66</v>
       </c>
       <c r="D33">
-        <f t="shared" si="3"/>
-        <v>175.26</v>
+        <v>69</v>
       </c>
       <c r="E33">
-        <f t="shared" si="3"/>
-        <v>182.88</v>
+        <v>72</v>
       </c>
       <c r="F33">
-        <f t="shared" si="3"/>
-        <v>187.96</v>
+        <v>74</v>
       </c>
       <c r="G33">
-        <f t="shared" si="3"/>
-        <v>193.04</v>
+        <v>76</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="C34">
-        <v>64</v>
-      </c>
-      <c r="D34">
-        <v>66</v>
-      </c>
-      <c r="E34">
-        <v>69</v>
-      </c>
-      <c r="F34">
-        <v>72</v>
-      </c>
-      <c r="G34">
-        <v>73</v>
+      <c r="A34" t="s">
+        <v>86</v>
+      </c>
+      <c r="B34" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="B35" t="s">
-        <v>49</v>
-      </c>
-      <c r="C35">
-        <v>66</v>
-      </c>
-      <c r="D35">
-        <v>69</v>
-      </c>
-      <c r="E35">
-        <v>72</v>
-      </c>
-      <c r="F35">
-        <v>74</v>
-      </c>
-      <c r="G35">
-        <v>76</v>
+        <v>89</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="B36" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>88</v>
+        <v>50</v>
       </c>
       <c r="B37" t="s">
-        <v>89</v>
+        <v>51</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>90</v>
-      </c>
-      <c r="B38" t="s">
-        <v>91</v>
+        <v>52</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>50</v>
-      </c>
-      <c r="B39" t="s">
-        <v>51</v>
+        <v>53</v>
+      </c>
+      <c r="B39">
+        <v>30</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>52</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>92</v>
+        <v>54</v>
+      </c>
+      <c r="B40">
+        <v>55</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B41">
-        <v>30</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>54</v>
-      </c>
-      <c r="B42">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>55</v>
-      </c>
-      <c r="B43">
-        <v>2.35</v>
+        <v>57</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>58</v>
+        <v>60</v>
+      </c>
+      <c r="B46">
+        <v>142</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>59</v>
+        <v>61</v>
+      </c>
+      <c r="B47">
+        <v>100</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>60</v>
-      </c>
-      <c r="B48">
-        <v>142</v>
+        <v>62</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>61</v>
-      </c>
-      <c r="B49">
-        <v>100</v>
+        <v>63</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>62</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>100</v>
+        <v>64</v>
+      </c>
+      <c r="B50">
+        <v>31.6</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>63</v>
+        <v>65</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B52">
-        <v>31.6</v>
+        <v>48</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B54">
-        <v>48</v>
+        <v>160</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>67</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>101</v>
+        <v>69</v>
+      </c>
+      <c r="B55">
+        <v>160</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>68</v>
-      </c>
-      <c r="B56">
-        <v>160</v>
+        <v>70</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>69</v>
-      </c>
-      <c r="B57">
-        <v>160</v>
+        <v>71</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>70</v>
+        <v>72</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>92</v>
@@ -1508,39 +1494,39 @@
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>73</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>92</v>
+        <v>75</v>
+      </c>
+      <c r="B61">
+        <v>2</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>74</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>92</v>
+        <v>76</v>
+      </c>
+      <c r="B62">
+        <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>75</v>
-      </c>
-      <c r="B63">
-        <v>2</v>
+        <v>77</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>76</v>
-      </c>
-      <c r="B64">
-        <v>1</v>
+        <v>78</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>92</v>
@@ -1548,7 +1534,7 @@
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>92</v>
@@ -1556,7 +1542,7 @@
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>92</v>
@@ -1564,47 +1550,31 @@
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>80</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>92</v>
+        <v>82</v>
+      </c>
+      <c r="B68">
+        <v>3035</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>81</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>82</v>
-      </c>
-      <c r="B70">
-        <v>3035</v>
+        <v>84</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A72" t="s">
-        <v>84</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A73" t="s">
         <v>85</v>
       </c>
-      <c r="B73" s="1" t="s">
-        <v>102</v>
+      <c r="B71" s="1" t="s">
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Rodeo Labs TrailDonkey 4.2 2025.xlsx
+++ b/data/gravel/Rodeo Labs TrailDonkey 4.2 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E77AE10-EE8E-5A48-8402-28C744EB2A8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7486ADAA-2298-6449-A174-11271BE1AB85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29460" yWindow="-19840" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7320" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="106">
   <si>
     <t>brand</t>
   </si>
@@ -335,9 +335,6 @@
     <t>50/34</t>
   </si>
   <si>
-    <t>usd</t>
-  </si>
-  <si>
     <t>Rodeo Labs</t>
   </si>
   <si>
@@ -345,6 +342,15 @@
   </si>
   <si>
     <t>a8:g31</t>
+  </si>
+  <si>
+    <t>USD</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Denver, Colorado, USA</t>
   </si>
 </sst>
 </file>
@@ -699,7 +705,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G71"/>
+  <dimension ref="A1:G72"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -710,7 +716,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
@@ -747,7 +753,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -755,7 +761,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="22" x14ac:dyDescent="0.3">
@@ -1574,7 +1580,15 @@
         <v>85</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>100</v>
+        <v>103</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>104</v>
+      </c>
+      <c r="B72" t="s">
+        <v>105</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Rodeo Labs TrailDonkey 4.2 2025.xlsx
+++ b/data/gravel/Rodeo Labs TrailDonkey 4.2 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7486ADAA-2298-6449-A174-11271BE1AB85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF3EF7C0-B3DD-9646-92E4-D6883556ED2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7320" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="112">
   <si>
     <t>brand</t>
   </si>
@@ -351,6 +351,24 @@
   </si>
   <si>
     <t>Denver, Colorado, USA</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -705,7 +723,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G72"/>
+  <dimension ref="A1:G78"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1402,129 +1420,111 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>62</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>63</v>
+        <v>107</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>64</v>
-      </c>
-      <c r="B50">
-        <v>31.6</v>
+        <v>108</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>65</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>66</v>
-      </c>
-      <c r="B52">
-        <v>48</v>
+        <v>110</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>67</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>68</v>
-      </c>
-      <c r="B54">
-        <v>160</v>
+        <v>62</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>69</v>
-      </c>
-      <c r="B55">
-        <v>160</v>
+        <v>63</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>70</v>
+        <v>64</v>
+      </c>
+      <c r="B56">
+        <v>31.6</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>72</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>92</v>
+        <v>66</v>
+      </c>
+      <c r="B58">
+        <v>48</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>74</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>92</v>
+        <v>68</v>
+      </c>
+      <c r="B60">
+        <v>160</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="B61">
-        <v>2</v>
+        <v>160</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>76</v>
-      </c>
-      <c r="B62">
-        <v>1</v>
+        <v>70</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>92</v>
@@ -1532,7 +1532,7 @@
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>92</v>
@@ -1540,7 +1540,7 @@
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>92</v>
@@ -1548,28 +1548,31 @@
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>81</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>92</v>
+        <v>75</v>
+      </c>
+      <c r="B67">
+        <v>2</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="B68">
-        <v>3035</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>83</v>
+        <v>77</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>92</v>
@@ -1577,17 +1580,62 @@
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
+        <v>80</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>81</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>82</v>
+      </c>
+      <c r="B74">
+        <v>3035</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>84</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>85</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
         <v>104</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B78" t="s">
         <v>105</v>
       </c>
     </row>
